--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261002_232559.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261002_232559.xlsx
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261002_232559.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261002_232559.xlsx
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
